--- a/data/trans_dic/P36BPD13_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,67; 97,7</t>
+          <t>92,43; 97,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97,35; 99,34</t>
+          <t>97,31; 99,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,55; 98,25</t>
+          <t>95,33; 98,27</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,12; 67,09</t>
+          <t>55,71; 66,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,25; 78,9</t>
+          <t>72,48; 79,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,36; 71,79</t>
+          <t>65,32; 72,12</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,57; 88,96</t>
+          <t>81,01; 89,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,83; 93,26</t>
+          <t>87,97; 93,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,92; 90,62</t>
+          <t>85,94; 90,59</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,91; 93,52</t>
+          <t>84,83; 93,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,17; 97,36</t>
+          <t>93,28; 97,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,68; 95,29</t>
+          <t>90,88; 95,51</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,81; 99,01</t>
+          <t>94,93; 99,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,6; 97,16</t>
+          <t>92,32; 97,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,7; 97,67</t>
+          <t>94,66; 97,66</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,16; 95,23</t>
+          <t>89,12; 95,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,76; 97,85</t>
+          <t>93,75; 97,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,56; 96,03</t>
+          <t>92,49; 96,08</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,29; 82,67</t>
+          <t>75,19; 82,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,03; 92,98</t>
+          <t>79,27; 92,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,92; 89,5</t>
+          <t>78,85; 89,44</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>90,16; 96,96</t>
+          <t>90,15; 96,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,82; 91,15</t>
+          <t>86,75; 90,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,49; 94,71</t>
+          <t>89,55; 94,81</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,51</t>
+          <t>83,39; 88,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,73; 90,99</t>
+          <t>87,72; 90,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86,04; 89,2</t>
+          <t>86,06; 88,86</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>287196; 302793</t>
+          <t>286461; 302330</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>281964; 287722</t>
+          <t>281836; 287714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>572891; 589034</t>
+          <t>571547; 589163</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>290204; 346953</t>
+          <t>288093; 345706</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>371570; 405777</t>
+          <t>372764; 406855</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>674159; 740410</t>
+          <t>673693; 743915</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>248136; 273965</t>
+          <t>249474; 274581</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>299734; 318234</t>
+          <t>300188; 318619</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>557810; 588348</t>
+          <t>557943; 588136</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>263452; 290164</t>
+          <t>263183; 289172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>440192; 459991</t>
+          <t>440699; 459526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>709758; 745827</t>
+          <t>711309; 747550</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>168821; 176300</t>
+          <t>169036; 176556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>192159; 201630</t>
+          <t>191579; 201619</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>365170; 376621</t>
+          <t>365001; 376564</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>239613; 255932</t>
+          <t>239521; 256344</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>241017; 251525</t>
+          <t>240983; 251148</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>486702; 504950</t>
+          <t>486333; 505225</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>467368; 513225</t>
+          <t>466757; 513244</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>661304; 778076</t>
+          <t>663350; 776408</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1150360; 1304501</t>
+          <t>1149250; 1303662</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>835782; 898817</t>
+          <t>835641; 896943</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>621930; 652995</t>
+          <t>621481; 651833</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1470621; 1556355</t>
+          <t>1471576; 1558131</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2875657; 3044662</t>
+          <t>2868463; 3037284</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3189337; 3307672</t>
+          <t>3188872; 3303712</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6087588; 6310817</t>
+          <t>6088937; 6286971</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD13_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,43; 97,55</t>
+          <t>93,83; 98,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97,31; 99,34</t>
+          <t>96,92; 99,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,33; 98,27</t>
+          <t>96,0; 98,31</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,71; 66,85</t>
+          <t>56,23; 66,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,48; 79,11</t>
+          <t>71,53; 78,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,32; 72,12</t>
+          <t>65,18; 71,49</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,01; 89,16</t>
+          <t>81,28; 89,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,97; 93,37</t>
+          <t>87,92; 93,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,94; 90,59</t>
+          <t>85,94; 90,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,83; 93,2</t>
+          <t>84,76; 92,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,28; 97,26</t>
+          <t>91,7; 95,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,88; 95,51</t>
+          <t>89,33; 93,93</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,93; 99,15</t>
+          <t>95,33; 98,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,32; 97,16</t>
+          <t>93,23; 97,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,66; 97,66</t>
+          <t>95,13; 97,71</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,12; 95,38</t>
+          <t>89,12; 95,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,75; 97,7</t>
+          <t>94,21; 97,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,49; 96,08</t>
+          <t>92,69; 96,22</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,19; 82,68</t>
+          <t>76,42; 83,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,27; 92,78</t>
+          <t>77,67; 82,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,85; 89,44</t>
+          <t>77,81; 82,04</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>90,15; 96,76</t>
+          <t>88,1; 92,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,75; 90,99</t>
+          <t>87,32; 91,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,55; 94,81</t>
+          <t>88,35; 91,26</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>83,39; 88,3</t>
+          <t>83,14; 85,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,72; 90,88</t>
+          <t>86,82; 88,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86,06; 88,86</t>
+          <t>85,35; 87,03</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>296726</t>
+          <t>306361</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>285484</t>
+          <t>310833</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>582210</t>
+          <t>617194</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>286461; 302330</t>
+          <t>298020; 311601</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>281836; 287714</t>
+          <t>306341; 313475</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>571547; 589163</t>
+          <t>608347; 622962</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>318128</t>
+          <t>325268</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>390505</t>
+          <t>410827</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>708634</t>
+          <t>736095</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>288093; 345706</t>
+          <t>297647; 350226</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>372764; 406855</t>
+          <t>390420; 428721</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>673693; 743915</t>
+          <t>700816; 768660</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>263453</t>
+          <t>262457</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>310675</t>
+          <t>316504</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574128</t>
+          <t>578961</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>249474; 274581</t>
+          <t>250348; 274844</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300188; 318619</t>
+          <t>305592; 324817</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>557943; 588136</t>
+          <t>563405; 594211</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>278413</t>
+          <t>331623</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>450301</t>
+          <t>392894</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>728714</t>
+          <t>724516</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>263183; 289172</t>
+          <t>314046; 344430</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>440699; 459526</t>
+          <t>383723; 399593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>711309; 747550</t>
+          <t>704770; 741074</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>173856</t>
+          <t>200292</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>198036</t>
+          <t>215926</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371892</t>
+          <t>416217</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>169036; 176556</t>
+          <t>195354; 202869</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>191579; 201619</t>
+          <t>210747; 219523</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>365001; 376564</t>
+          <t>409994; 421108</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>249338</t>
+          <t>250619</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>247441</t>
+          <t>254232</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>496778</t>
+          <t>504851</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>239521; 256344</t>
+          <t>240521; 256922</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240983; 251148</t>
+          <t>248479; 257912</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>486333; 505225</t>
+          <t>494635; 513477</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>491666</t>
+          <t>570928</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>712357</t>
+          <t>609092</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1204022</t>
+          <t>1180020</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>466757; 513244</t>
+          <t>546419; 597018</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>663350; 776408</t>
+          <t>588407; 628430</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1149250; 1303662</t>
+          <t>1145823; 1208162</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>865026</t>
+          <t>720829</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>638858</t>
+          <t>741392</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1503884</t>
+          <t>1462221</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>835641; 896943</t>
+          <t>701430; 736249</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>621481; 651833</t>
+          <t>724646; 757977</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1471576; 1558131</t>
+          <t>1436499; 1483934</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2936605</t>
+          <t>2968376</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3233657</t>
+          <t>3251699</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6170262</t>
+          <t>6220076</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2868463; 3037284</t>
+          <t>2919385; 3018999</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3188872; 3303712</t>
+          <t>3216731; 3288283</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6088937; 6286971</t>
+          <t>6159518; 6280462</t>
         </is>
       </c>
     </row>
